--- a/output/review/local-2026-03-21/hemoglobin_review.xlsx
+++ b/output/review/local-2026-03-21/hemoglobin_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hemoglobin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'hemoglobin'!$A$12:$K$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'hemoglobin'!$A$12:$L$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,59 +593,65 @@
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
       <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>LOINC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>SCTID</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>FSN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Complete aggregation</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Quantitative (all numeric)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Quantitative &amp; convertible</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Qualitative (ordinal / nominal / presence)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Semi-quantitative (test strip)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Panel / order code (no Property)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Use case</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -653,27 +660,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>717-9</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>186111010000103</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Blood</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -681,14 +688,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -696,12 +703,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -710,27 +722,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>33517-4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>113801010000100</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in body fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Body fluid</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -738,14 +750,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -753,12 +765,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -767,27 +784,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>48035-0</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>141941010000104</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in cerebrospinal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Cerebral spinal fluid</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -795,14 +812,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -810,12 +827,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -824,27 +846,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>2334-1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>832611010000109</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in gast fld^Patient.gastrointestinal at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Gastric fluid from gastrointestinal</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -852,14 +874,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -867,12 +889,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -881,27 +908,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>42909-2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>839561010000104</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in gast fld^Patient.gastrointestinal at point in time 1st specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Gastric fluid from gastrointestinal --1st specimen</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -909,14 +936,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -924,12 +951,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -938,27 +970,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>42910-0</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>839571010000109</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in gast fld^Patient.gastrointestinal at point in time 2nd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Gastric fluid from gastrointestinal --2nd specimen</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -966,14 +998,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -981,12 +1013,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -995,27 +1032,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>42911-8</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>839581010000107</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in gast fld^Patient.gastrointestinal at point in time 3rd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Gastric fluid from gastrointestinal --3rd specimen</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1023,14 +1060,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1038,12 +1075,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1052,27 +1094,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>34618-9</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>145031010000105</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in specimen at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Specimen</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1080,14 +1122,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1095,12 +1137,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1109,27 +1156,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>50017-3</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>844281010000109</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Sputum/Gast fld^Patient.gastrointestinal at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Sputum or Gastric fluid from gastrointestinal</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1137,14 +1184,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1152,12 +1199,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1166,27 +1218,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>2335-8</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>832621010000103</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1194,14 +1246,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -1209,12 +1261,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1223,27 +1280,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14563-1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>829271010000108</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time 1st specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal --1st specimen</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1251,14 +1308,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -1266,12 +1323,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1280,27 +1342,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14564-9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>829281010000106</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time 2nd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal --2nd specimen</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1308,14 +1370,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1323,12 +1385,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1337,27 +1404,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14565-6</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>829291010000109</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time 3rd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal --3rd specimen</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1365,14 +1432,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -1380,12 +1447,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1394,27 +1466,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12503-9</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>828341010000100</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time 4th specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal --4th specimen</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1422,14 +1494,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -1437,12 +1509,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1451,27 +1528,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12504-7</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>828351010000103</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time 5th specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal --5th specimen</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1479,14 +1556,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -1494,12 +1571,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1508,27 +1590,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>27401-9</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>833961010000106</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time 6th specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal --6th specimen</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1536,14 +1618,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -1551,12 +1633,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1565,27 +1652,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>27925-7</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>834041010000109</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time 7th specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal --7th specimen</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1593,14 +1680,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -1608,12 +1695,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1622,27 +1714,27 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>27926-5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>834051010000106</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time 8th specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal --8th specimen</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1650,14 +1742,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -1665,12 +1757,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1679,27 +1776,27 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>80372-6</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>855941010000107</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal at point in time by rapid immunoassay (observable entity)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal by Rapid immunoassay</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1707,14 +1804,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1722,12 +1819,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1736,27 +1838,27 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>104738-0</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>824631010000108</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal.lower at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal lower</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1764,14 +1866,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1779,12 +1881,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1793,27 +1900,27 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>29771-3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>834201010000103</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal.lower at point in time by immunoassay (observable entity)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal lower by Immunoassay</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1821,14 +1928,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -1836,12 +1943,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1850,27 +1962,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>57905-2</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>848921010000108</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal.lower at point in time by immunoassay 1st specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal lower by Immunoassay --1st specimen</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1878,14 +1990,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -1893,12 +2005,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1907,27 +2024,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>56490-6</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>848171010000106</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal.lower at point in time by immunoassay 2nd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal lower by Immunoassay --2nd specimen</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1935,14 +2052,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -1950,12 +2067,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -1964,27 +2086,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>56491-4</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>848181010000109</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Stool^Patient.gastrointestinal.lower at point in time by immunoassay 3rd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Stool from gastrointestinal lower by Immunoassay --3rd specimen</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1992,14 +2114,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2007,12 +2129,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -2021,27 +2148,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>725-2</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>111791010000102</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Urine</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2049,14 +2176,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -2064,12 +2191,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -2078,27 +2210,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>57751-0</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>43271010000109</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in urine at point in time by automated test strip (observable entity)</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Urine by Automated test strip</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2106,14 +2238,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2121,12 +2253,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -2135,27 +2272,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>5794-3</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>246811010000100</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in urine at point in time by test strip (observable entity)</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Urine by Test strip</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2163,14 +2300,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2178,12 +2315,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -2192,27 +2334,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>48047-5</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>842371010000105</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in Vomitus^Patient.gastrointestinal at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Vomitus from gastrointestinal</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2220,14 +2362,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -2235,12 +2377,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -2249,27 +2396,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>42912-6</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>839591010000105</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in XXX^Patient.gastrointestinal at point in time 2nd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Specimen from gastrointestinal --2nd specimen</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2277,14 +2424,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2292,12 +2439,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -2306,27 +2458,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>42913-4</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>839601010000104</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Presence of hemoglobin in XXX^Patient.gastrointestinal.lower at point in time 1st specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Presence] in Specimen from gastrointestinal lower --1st specimen</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2334,14 +2486,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2349,12 +2501,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -2363,32 +2520,32 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>59468-9</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>599241010000109</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Entitic amount of substance of hemoglobin in erythrocyte at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>MCH [Entitic substance]</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -2406,12 +2563,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2420,32 +2582,32 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>73895-5</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>609901010000107</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Entitic amount of substance of hemoglobin in retic at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Entitic substance] in Reticulocytes by Automated count</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -2463,12 +2625,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2477,32 +2644,32 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>28539-5</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>521361010000106</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Entitic mass of hemoglobin in erythrocyte at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>MCH [Entitic mass]</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -2520,12 +2687,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2534,32 +2706,32 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>785-6</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>612991010000106</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Entitic mass of hemoglobin in erythrocyte at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>MCH [Entitic mass] by Automated count</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -2577,12 +2749,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2591,32 +2768,32 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>47278-7</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>559591010000107</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Entitic mass of hemoglobin in RBC^BldCo at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>MCH [Entitic mass] in Cord blood</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -2634,12 +2811,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2648,32 +2830,32 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>62243-1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>602571010000101</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Entitic mass of hemoglobin in RBC^Fetus at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>MCH [Entitic mass] in Fetus by Automated count</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -2691,12 +2873,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2705,32 +2892,32 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>42810-2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>552221010000102</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Entitic mass of hemoglobin in retic at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Entitic mass] in Reticulocytes</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -2748,12 +2935,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2762,32 +2954,32 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>71694-4</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>608081010000109</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Entitic mass of hemoglobin in retic at point in time by automated count (observable entity)</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Entitic mass] in Reticulocytes by Automated count</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -2805,12 +2997,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2819,32 +3016,32 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>27396-1</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>833951010000109</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Mass content of hemoglobin in Stool^Patient.gastrointestinal at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/mass] in Stool from gastrointestinal</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2862,12 +3059,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2876,32 +3078,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24469-9</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>832861010000108</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of hemoglobin to hemoglobin.total in blood at point in time by electrophoresis (observable entity)</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin XXX/Hemoglobin.total in Blood by Electrophoresis</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -2919,12 +3121,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2933,32 +3140,32 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>48343-8</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>562251010000100</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of hemoglobin.other to hemoglobin.total in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin.other/Hemoglobin.total in Blood</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2976,12 +3183,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -2990,32 +3202,32 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>32017-6</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>527101010000100</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of hemoglobin.other to hemoglobin.total in blood at point in time by electrophoresis (observable entity)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin.other/Hemoglobin.total in Blood by Electrophoresis</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3033,12 +3245,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3047,32 +3264,32 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>42248-5</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>551191010000101</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of hemoglobin.other to hemoglobin.total in blood at point in time by high pressure liquid chromatography (observable entity)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin.other/Hemoglobin.total in Blood by HPLC</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3090,12 +3307,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -3104,32 +3326,32 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>109484-6</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>719011010000100</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Measurement of hemoglobin in arterial blood (observable entity)</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Measurement] in Arterial blood</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3147,12 +3369,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -3161,32 +3388,32 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>110885-1</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>728771010000107</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Measurement of hemoglobin in blood (observable entity)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Measurement] in Blood</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3204,12 +3431,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -3218,32 +3450,32 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>109887-0</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>721771010000103</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Measurement of hemoglobin in mixed venous blood (observable entity)</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Measurement] in Mixed venous blood</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -3261,12 +3493,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -3275,32 +3512,32 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>109886-2</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>721761010000108</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Measurement of hemoglobin in venous blood (observable entity)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Measurement] in Venous blood</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -3318,12 +3555,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -3332,24 +3574,24 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>30313-1</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>103141010000106</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in arterial blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Arterial blood</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3360,9 +3602,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3375,12 +3617,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3389,24 +3636,24 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>14775-1</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>211871010000107</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in arterial blood at point in time by oximetry (observable entity)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Arterial blood by Oximetry</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3417,9 +3664,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3432,12 +3679,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3446,24 +3698,24 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>30354-5</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>240741010000109</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in arterial cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Arterial cord blood</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3474,9 +3726,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3489,12 +3741,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3503,24 +3760,24 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>33026-6</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>252711010000109</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in arterial cord blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Arterial cord blood by calculation</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3531,9 +3788,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3546,12 +3803,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3560,24 +3822,24 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>54289-4</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>241521010000102</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in Bld^BPU at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Blood from Blood product unit</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3588,9 +3850,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3603,12 +3865,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3617,24 +3884,24 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>61180-6</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>91561010000106</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in Bld^Fetus at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Blood from Fetus</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3645,9 +3912,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -3660,12 +3927,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3674,24 +3946,24 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>97550-8</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>98801010000104</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in BldCV at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Central venous blood by calculation</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3702,9 +3974,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3717,12 +3989,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3731,24 +4008,24 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>97555-7</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>269771010000102</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in BldCV at point in time by oximetry (observable entity)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Central venous blood by Oximetry</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3759,9 +4036,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3774,12 +4051,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3788,24 +4070,24 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>718-7</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>168331010000106</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Blood</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3816,9 +4098,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3831,12 +4113,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3845,24 +4132,24 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>20509-6</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>66931010000104</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Blood by calculation</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3873,9 +4160,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3888,12 +4175,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3902,24 +4194,24 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>55782-7</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>204121010000101</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in blood at point in time by oximetry (observable entity)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Blood by Oximetry</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3930,9 +4222,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3945,12 +4237,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -3959,24 +4256,24 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>48725-6</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>67261010000101</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in blood at point in time pre therapeutic phlebotomy (observable entity)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Blood --pre therapeutic phlebotomy</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3987,9 +4284,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -4002,12 +4299,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4016,24 +4318,24 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>33509-1</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>190711010000102</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in body fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Body fluid</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4044,9 +4346,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -4059,12 +4361,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4073,24 +4380,24 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>30352-9</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>143151010000100</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in capillary blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Capillary blood</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4101,9 +4408,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -4116,12 +4423,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4130,24 +4442,24 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>97556-5</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>122541010000102</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in capillary blood at point in time by oximetry (observable entity)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Capillary blood by Oximetry</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4158,9 +4470,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -4173,12 +4485,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4187,24 +4504,24 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>719-5</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>41781010000101</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in cerebrospinal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Cerebral spinal fluid</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4215,9 +4532,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -4230,12 +4547,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4244,24 +4566,24 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>40719-7</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>185861010000101</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Cord blood</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4272,9 +4594,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -4287,12 +4609,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4301,24 +4628,24 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>30351-1</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>157231010000106</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in mixed venous blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Mixed venous blood</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4329,9 +4656,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -4344,12 +4671,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4358,24 +4690,24 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>105040-0</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>483971010000104</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in mixed venous blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Mixed venous blood by calculation</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4386,9 +4718,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4401,12 +4733,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4415,24 +4752,24 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>76768-1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>160411010000108</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in mixed venous blood at point in time by oximetry (observable entity)</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Mixed venous blood by Oximetry</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4443,9 +4780,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -4458,12 +4795,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4472,24 +4814,24 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>69950-4</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>108391010000106</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in pericardial fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Pericardial fluid</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4500,9 +4842,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -4515,12 +4857,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4529,24 +4876,24 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>723-7</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>149081010000108</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in peritoneal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Peritoneal fluid</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4557,9 +4904,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -4572,12 +4919,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4586,24 +4938,24 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>722-9</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>195541010000103</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in pleural fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Pleural fluid</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4614,9 +4966,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -4629,12 +4981,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4643,24 +5000,24 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>107191-9</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>825501010000104</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in Stool^Patient.gastrointestinal at point in time 1st specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Stool from gastrointestinal --1st specimen</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4671,9 +5028,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -4686,12 +5043,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4700,24 +5062,24 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>107190-1</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>825491010000105</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in Stool^Patient.gastrointestinal at point in time 2nd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Stool from gastrointestinal --2nd specimen</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4728,9 +5090,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -4743,12 +5105,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4757,24 +5124,24 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>107189-3</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>825481010000107</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in Stool^Patient.gastrointestinal at point in time 3rd specimen (observable entity)</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Stool from gastrointestinal --3rd specimen</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4785,9 +5152,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -4800,12 +5167,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4814,24 +5186,24 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>58453-2</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>849041010000107</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in Stool^Patient.gastrointestinal.lower at point in time by immunoassay (observable entity)</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Stool from gastrointestinal lower by Immunoassay</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4842,9 +5214,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -4857,12 +5229,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4871,24 +5248,24 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>724-5</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>224421010000101</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in synovial fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Synovial fluid</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4899,9 +5276,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -4914,12 +5291,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4928,24 +5310,24 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>726-0</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>165951010000108</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in urine at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Urine</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4956,9 +5338,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -4971,12 +5353,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -4985,24 +5372,24 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>30350-3</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>198381010000105</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in venous blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Venous blood</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5013,9 +5400,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -5028,12 +5415,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5042,24 +5434,24 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>105274-5</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>484891010000107</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in venous blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Venous blood by calculation</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5070,9 +5462,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -5085,12 +5477,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5099,24 +5496,24 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>76769-9</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>89311010000104</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in venous blood at point in time by oximetry (observable entity)</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Venous blood by Oximetry</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5127,9 +5524,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -5142,12 +5539,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5156,24 +5558,24 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>30353-7</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>259921010000108</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in venous cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Venous cord blood</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5184,9 +5586,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -5199,12 +5601,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5213,24 +5620,24 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>33025-8</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>108491010000103</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in venous cord blood at point in time by calculation (observable entity)</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Venous cord blood by calculation</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5241,9 +5648,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -5256,12 +5663,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5270,24 +5682,24 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>35183-3</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>738931010000109</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Mass concentration or substance concentration of hemoglobin in plasma at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass or Moles/volume] in Plasma</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5298,9 +5710,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -5313,12 +5725,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J95" s="2" t="inlineStr">
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5327,24 +5744,24 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>75928-2</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>241881010000100</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of hemoglobin in arterial blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Moles/volume] in Arterial blood</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5355,9 +5772,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -5370,12 +5787,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5384,24 +5806,24 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>59260-0</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>214131010000101</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of hemoglobin in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Moles/volume] in Blood</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5412,9 +5834,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -5427,12 +5849,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5441,24 +5868,24 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>105300-8</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>484911010000109</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of hemoglobin in mixed venous blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Moles/volume] in Mixed venous blood</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5469,9 +5896,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -5484,12 +5911,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5498,24 +5930,24 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>93846-4</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>151971010000108</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of hemoglobin in venous blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Moles/volume] in Venous blood</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5526,9 +5958,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -5541,12 +5973,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5555,24 +5992,24 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>103750-6</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>481881010000107</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of hemoglobin in venous cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Moles/volume] in Venous cord blood</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5583,9 +6020,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -5598,12 +6035,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr">
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -5612,27 +6054,27 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>50559-4</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>69741010000101</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in urine at point in time by automated test strip (observable entity)</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Urine by Automated test strip</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -5645,22 +6087,27 @@
           <t>·</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
         <is>
           <t>semiquantitative</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>Semi-quantitative scale (test strip)</t>
         </is>
@@ -5669,27 +6116,27 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>49137-3</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>75411010000104</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of hemoglobin in urine at point in time by test strip (observable entity)</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Hemoglobin [Mass/volume] in Urine by Test strip</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -5702,29 +6149,34 @@
           <t>·</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
         <is>
           <t>semiquantitative</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="L102" s="2" t="inlineStr">
         <is>
           <t>Semi-quantitative scale (test strip)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:K102"/>
+  <autoFilter ref="A12:L102"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>